--- a/publicdataexportv131450706334_with_lon_lat.xlsx
+++ b/publicdataexportv131450706334_with_lon_lat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baxe\Documents\Uni\AdvancedBA\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baxe\Documents\Uni\AdvancedBA\project\Critical-Energy-Infrastructure-Under-Hybrid-War-Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12333066-2686-444E-9C65-B7B297F6F39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0C2984-C92E-45AE-99F5-37BBC77E1B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-615" yWindow="465" windowWidth="17025" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="7920" windowWidth="14610" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -12136,16 +12136,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -12349,7 +12347,7 @@
     <col min="8" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12362,11 +12360,11 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -12388,14 +12386,14 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>4008</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>4009</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>76</v>
       </c>
@@ -12424,7 +12422,7 @@
         <v>55.457599999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>192</v>
       </c>
@@ -12453,7 +12451,7 @@
         <v>55.250725112358197</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>194</v>
       </c>
@@ -12475,10 +12473,10 @@
       <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>195</v>
       </c>
@@ -12507,7 +12505,7 @@
         <v>56.716000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>53</v>
       </c>
@@ -12536,7 +12534,7 @@
         <v>55.87</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>54</v>
       </c>
@@ -12564,9 +12562,8 @@
       <c r="I10" s="1">
         <v>55.665999999999997</v>
       </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>55</v>
       </c>
@@ -12595,7 +12592,7 @@
         <v>55.65</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>56</v>
       </c>
@@ -12624,7 +12621,7 @@
         <v>55.686799999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>57</v>
       </c>
@@ -12653,7 +12650,7 @@
         <v>55.686799999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>58</v>
       </c>
@@ -12682,7 +12679,7 @@
         <v>55.686799999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>196</v>
       </c>
@@ -12711,7 +12708,7 @@
         <v>55.469000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>197</v>
       </c>
@@ -13597,10 +13594,10 @@
         <v>14</v>
       </c>
       <c r="H46" s="1">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="I46" s="1">
-        <v>55.279000000000003</v>
+        <v>55.2357925836045</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -14124,8 +14121,12 @@
       <c r="G65" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+      <c r="H65" s="1">
+        <v>11.3484666229282</v>
+      </c>
+      <c r="I65" s="1">
+        <v>54.667257021721198</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
@@ -14932,7 +14933,7 @@
       <c r="I94" s="1">
         <v>55.660512088191503</v>
       </c>
-      <c r="J94" s="7"/>
+      <c r="J94" s="5"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
@@ -17189,8 +17190,12 @@
       <c r="G175" t="s">
         <v>14</v>
       </c>
-      <c r="H175" s="1"/>
-      <c r="I175" s="1"/>
+      <c r="H175" s="1">
+        <v>12.5493736552885</v>
+      </c>
+      <c r="I175" s="1">
+        <v>56.022795688424402</v>
+      </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
@@ -17616,8 +17621,12 @@
       <c r="G191" t="s">
         <v>14</v>
       </c>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
+      <c r="H191" s="1">
+        <v>11.6516548385523</v>
+      </c>
+      <c r="I191" s="1">
+        <v>55.547121160443297</v>
+      </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
@@ -17642,10 +17651,10 @@
         <v>14</v>
       </c>
       <c r="H192" s="1">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="I192" s="1">
-        <v>54.942999999999998</v>
+        <v>54.959195188550602</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -17754,10 +17763,10 @@
         <v>22</v>
       </c>
       <c r="H196" s="1">
-        <v>11.895</v>
+        <v>11.696333555734901</v>
       </c>
       <c r="I196" s="1">
-        <v>54.753</v>
+        <v>54.796410345953198</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -17783,10 +17792,10 @@
         <v>14</v>
       </c>
       <c r="H197" s="1">
-        <v>11.895</v>
+        <v>11.696333555734901</v>
       </c>
       <c r="I197" s="1">
-        <v>54.753</v>
+        <v>54.796410345953198</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -17869,8 +17878,12 @@
       <c r="G200" t="s">
         <v>31</v>
       </c>
-      <c r="H200" s="1"/>
-      <c r="I200" s="1"/>
+      <c r="H200" s="1">
+        <v>11.6329045846498</v>
+      </c>
+      <c r="I200" s="1">
+        <v>54.620413968645003</v>
+      </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
@@ -17894,8 +17907,12 @@
       <c r="G201" t="s">
         <v>31</v>
       </c>
-      <c r="H201" s="1"/>
-      <c r="I201" s="1"/>
+      <c r="H201" s="1">
+        <v>11.678968527806701</v>
+      </c>
+      <c r="I201" s="1">
+        <v>54.583058000506803</v>
+      </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
@@ -18417,8 +18434,12 @@
       <c r="G220" t="s">
         <v>14</v>
       </c>
-      <c r="H220" s="1"/>
-      <c r="I220" s="1"/>
+      <c r="H220" s="1">
+        <v>12.432880529585701</v>
+      </c>
+      <c r="I220" s="1">
+        <v>55.926535538909903</v>
+      </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
@@ -18692,8 +18713,12 @@
       <c r="G230" t="s">
         <v>14</v>
       </c>
-      <c r="H230" s="1"/>
-      <c r="I230" s="1"/>
+      <c r="H230" s="1">
+        <v>12.7085299819776</v>
+      </c>
+      <c r="I230" s="1">
+        <v>56.049355009063497</v>
+      </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
@@ -18714,8 +18739,12 @@
       <c r="G231" t="s">
         <v>14</v>
       </c>
-      <c r="H231" s="1"/>
-      <c r="I231" s="1"/>
+      <c r="H231" s="1">
+        <v>12.7085299819776</v>
+      </c>
+      <c r="I231" s="1">
+        <v>56.049355009063497</v>
+      </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232">
@@ -19541,8 +19570,12 @@
       <c r="G261" t="s">
         <v>14</v>
       </c>
-      <c r="H261" s="1"/>
-      <c r="I261" s="1"/>
+      <c r="H261" s="1">
+        <v>11.218752272214999</v>
+      </c>
+      <c r="I261" s="1">
+        <v>54.845109536907202</v>
+      </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262">

--- a/publicdataexportv131450706334_with_lon_lat.xlsx
+++ b/publicdataexportv131450706334_with_lon_lat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baxe\Documents\Uni\AdvancedBA\project\Critical-Energy-Infrastructure-Under-Hybrid-War-Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0C2984-C92E-45AE-99F5-37BBC77E1B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80AE12D-3A73-4BF3-A170-32FE4197603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="7920" windowWidth="14610" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12473,8 +12473,12 @@
       <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="H7" s="1">
+        <v>9.9070202402914394</v>
+      </c>
+      <c r="I7" s="1">
+        <v>57.021767387471101</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -13781,8 +13785,12 @@
       <c r="G53" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="H53" s="1">
+        <v>12.3850960105833</v>
+      </c>
+      <c r="I53" s="1">
+        <v>55.747187804005499</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
@@ -13835,8 +13843,12 @@
       <c r="G55" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="H55" s="1">
+        <v>12.4051289650067</v>
+      </c>
+      <c r="I55" s="1">
+        <v>55.7020042516207</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
@@ -14324,8 +14336,12 @@
       <c r="G72" t="s">
         <v>14</v>
       </c>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+      <c r="H72" s="1">
+        <v>12.297757830688701</v>
+      </c>
+      <c r="I72" s="1">
+        <v>55.599077862221797</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
@@ -14603,8 +14619,12 @@
       <c r="G82" t="s">
         <v>14</v>
       </c>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
+      <c r="H82" s="1">
+        <v>12.537175734942499</v>
+      </c>
+      <c r="I82" s="1">
+        <v>55.761187302595303</v>
+      </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
@@ -14628,8 +14648,12 @@
       <c r="G83" t="s">
         <v>14</v>
       </c>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
+      <c r="H83" s="1">
+        <v>12.537175734942499</v>
+      </c>
+      <c r="I83" s="1">
+        <v>55.761187302595303</v>
+      </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
@@ -14653,8 +14677,12 @@
       <c r="G84" t="s">
         <v>14</v>
       </c>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="H84" s="1">
+        <v>12.537175734942499</v>
+      </c>
+      <c r="I84" s="1">
+        <v>55.761187302595303</v>
+      </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
@@ -14678,8 +14706,12 @@
       <c r="G85" t="s">
         <v>14</v>
       </c>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
+      <c r="H85" s="1">
+        <v>12.537175734942499</v>
+      </c>
+      <c r="I85" s="1">
+        <v>55.761187302595303</v>
+      </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
@@ -14703,8 +14735,12 @@
       <c r="G86" t="s">
         <v>31</v>
       </c>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
+      <c r="H86" s="1">
+        <v>12.464263696279501</v>
+      </c>
+      <c r="I86" s="1">
+        <v>55.743290002461599</v>
+      </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
@@ -14844,8 +14880,12 @@
       <c r="G91" t="s">
         <v>89</v>
       </c>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
+      <c r="H91" s="1">
+        <v>10.168049999999999</v>
+      </c>
+      <c r="I91" s="1">
+        <v>56.190435518399497</v>
+      </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
@@ -14986,8 +15026,12 @@
       <c r="G96" t="s">
         <v>14</v>
       </c>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="H96" s="1">
+        <v>12.1048418993376</v>
+      </c>
+      <c r="I96" s="1">
+        <v>55.653009430117599</v>
+      </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
@@ -15069,8 +15113,12 @@
       <c r="G99" t="s">
         <v>14</v>
       </c>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="H99" s="1">
+        <v>11.342020991294801</v>
+      </c>
+      <c r="I99" s="1">
+        <v>55.521728734864503</v>
+      </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
@@ -15094,8 +15142,12 @@
       <c r="G100" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
+      <c r="H100" s="1">
+        <v>11.342020991294801</v>
+      </c>
+      <c r="I100" s="1">
+        <v>55.521728734864503</v>
+      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
@@ -15119,8 +15171,12 @@
       <c r="G101" t="s">
         <v>14</v>
       </c>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
+      <c r="H101" s="1">
+        <v>11.342020991294801</v>
+      </c>
+      <c r="I101" s="1">
+        <v>55.521728734864503</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
@@ -15173,8 +15229,12 @@
       <c r="G103" t="s">
         <v>22</v>
       </c>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
+      <c r="H103" s="1">
+        <v>9.9549057288360903</v>
+      </c>
+      <c r="I103" s="1">
+        <v>56.482077640062002</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
@@ -15314,8 +15374,12 @@
       <c r="G108" t="s">
         <v>89</v>
       </c>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
+      <c r="H108" s="1">
+        <v>10.1426557207713</v>
+      </c>
+      <c r="I108" s="1">
+        <v>56.149388309803101</v>
+      </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
@@ -15339,8 +15403,12 @@
       <c r="G109" t="s">
         <v>14</v>
       </c>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
+      <c r="H109" s="1">
+        <v>12.3880574948221</v>
+      </c>
+      <c r="I109" s="1">
+        <v>55.759540142334998</v>
+      </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
@@ -15364,8 +15432,12 @@
       <c r="G110" t="s">
         <v>14</v>
       </c>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
+      <c r="H110" s="1">
+        <v>12.356128903592101</v>
+      </c>
+      <c r="I110" s="1">
+        <v>55.659958967004201</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
@@ -15389,8 +15461,12 @@
       <c r="G111" t="s">
         <v>14</v>
       </c>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
+      <c r="H111" s="1">
+        <v>12.227285618955399</v>
+      </c>
+      <c r="I111" s="1">
+        <v>55.789304084629499</v>
+      </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
@@ -15414,8 +15490,12 @@
       <c r="G112" t="s">
         <v>140</v>
       </c>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
+      <c r="H112" s="1">
+        <v>12.227285618955399</v>
+      </c>
+      <c r="I112" s="1">
+        <v>55.789304084629499</v>
+      </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
@@ -15468,8 +15548,12 @@
       <c r="G114" t="s">
         <v>14</v>
       </c>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
+      <c r="H114" s="1">
+        <v>9.9145827650929803</v>
+      </c>
+      <c r="I114" s="1">
+        <v>57.046325398949499</v>
+      </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
@@ -15863,8 +15947,12 @@
       <c r="G128" t="s">
         <v>14</v>
       </c>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
+      <c r="H128" s="1">
+        <v>12.6541582684112</v>
+      </c>
+      <c r="I128" s="1">
+        <v>55.634572192308603</v>
+      </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
@@ -15917,8 +16005,12 @@
       <c r="G130" t="s">
         <v>14</v>
       </c>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
+      <c r="H130" s="1">
+        <v>12.120777638837399</v>
+      </c>
+      <c r="I130" s="1">
+        <v>55.647621523041501</v>
+      </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
@@ -16435,8 +16527,12 @@
       <c r="G148" t="s">
         <v>14</v>
       </c>
-      <c r="H148" s="1"/>
-      <c r="I148" s="1"/>
+      <c r="H148" s="1">
+        <v>11.8863748101793</v>
+      </c>
+      <c r="I148" s="1">
+        <v>55.624854082792602</v>
+      </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
@@ -16717,8 +16813,12 @@
       <c r="G158" t="s">
         <v>89</v>
       </c>
-      <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
+      <c r="H158" s="1">
+        <v>8.3532261843899693</v>
+      </c>
+      <c r="I158" s="1">
+        <v>56.109386615118403</v>
+      </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
@@ -16945,8 +17045,12 @@
       <c r="G166" t="s">
         <v>22</v>
       </c>
-      <c r="H166" s="1"/>
-      <c r="I166" s="1"/>
+      <c r="H166" s="1">
+        <v>10.4987386757303</v>
+      </c>
+      <c r="I166" s="1">
+        <v>56.435023192998003</v>
+      </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
@@ -17086,8 +17190,12 @@
       <c r="G171" t="s">
         <v>22</v>
       </c>
-      <c r="H171" s="1"/>
-      <c r="I171" s="1"/>
+      <c r="H171" s="1">
+        <v>10.219010741370701</v>
+      </c>
+      <c r="I171" s="1">
+        <v>56.225273912856998</v>
+      </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
@@ -17111,8 +17219,12 @@
       <c r="G172" t="s">
         <v>22</v>
       </c>
-      <c r="H172" s="1"/>
-      <c r="I172" s="1"/>
+      <c r="H172" s="1">
+        <v>10.0985712474414</v>
+      </c>
+      <c r="I172" s="1">
+        <v>56.429767245475198</v>
+      </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
@@ -17165,8 +17277,12 @@
       <c r="G174" t="s">
         <v>14</v>
       </c>
-      <c r="H174" s="1"/>
-      <c r="I174" s="1"/>
+      <c r="H174" s="1">
+        <v>12.2742303637046</v>
+      </c>
+      <c r="I174" s="1">
+        <v>55.568545162906503</v>
+      </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
@@ -17430,8 +17546,12 @@
       <c r="G184" t="s">
         <v>14</v>
       </c>
-      <c r="H184" s="1"/>
-      <c r="I184" s="1"/>
+      <c r="H184" s="1">
+        <v>11.1176852759734</v>
+      </c>
+      <c r="I184" s="1">
+        <v>55.687374583797798</v>
+      </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
@@ -17679,8 +17799,12 @@
       <c r="G193" t="s">
         <v>14</v>
       </c>
-      <c r="H193" s="1"/>
-      <c r="I193" s="1"/>
+      <c r="H193" s="1">
+        <v>11.9453047753712</v>
+      </c>
+      <c r="I193" s="1">
+        <v>55.670574416635198</v>
+      </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
@@ -18081,8 +18205,12 @@
       <c r="G207" t="s">
         <v>22</v>
       </c>
-      <c r="H207" s="1"/>
-      <c r="I207" s="1"/>
+      <c r="H207" s="1">
+        <v>9.7322488134917098</v>
+      </c>
+      <c r="I207" s="1">
+        <v>55.598431048706303</v>
+      </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
@@ -18280,8 +18408,12 @@
       <c r="G214" t="s">
         <v>22</v>
       </c>
-      <c r="H214" s="1"/>
-      <c r="I214" s="1"/>
+      <c r="H214" s="1">
+        <v>9.9317093305177107</v>
+      </c>
+      <c r="I214" s="1">
+        <v>57.071587787009399</v>
+      </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
@@ -18334,8 +18466,12 @@
       <c r="G216" t="s">
         <v>14</v>
       </c>
-      <c r="H216" s="1"/>
-      <c r="I216" s="1"/>
+      <c r="H216" s="1">
+        <v>12.5878763748329</v>
+      </c>
+      <c r="I216" s="1">
+        <v>55.714479744646098</v>
+      </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
@@ -19239,10 +19375,10 @@
         <v>14</v>
       </c>
       <c r="H249" s="1">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="I249" s="1">
-        <v>55.628999999999998</v>
+        <v>55.656374272645202</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">

--- a/publicdataexportv131450706334_with_lon_lat.xlsx
+++ b/publicdataexportv131450706334_with_lon_lat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baxe\Documents\Uni\AdvancedBA\project\Critical-Energy-Infrastructure-Under-Hybrid-War-Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80AE12D-3A73-4BF3-A170-32FE4197603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365A0E68-7859-4853-BB1A-DE7DE2FB6251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="7920" windowWidth="14610" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="Shunt" sheetId="7" r:id="rId7"/>
     <sheet name="HVDC" sheetId="8" r:id="rId8"/>
     <sheet name="PFModelInfo" sheetId="9" r:id="rId9"/>
-    <sheet name="Ark1" sheetId="10" r:id="rId10"/>
-    <sheet name="Ark2" sheetId="11" r:id="rId11"/>
-    <sheet name="Ark3" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -12341,10 +12338,13 @@
   <dimension ref="A1:J304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
     <col min="4" max="4" width="31.5703125" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -20753,33 +20753,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20788,6 +20761,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -34451,6 +34432,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -39008,6 +38999,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M394"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -52840,6 +52836,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -55445,6 +55446,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -58946,6 +58950,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/publicdataexportv131450706334_with_lon_lat.xlsx
+++ b/publicdataexportv131450706334_with_lon_lat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baxe\Documents\Uni\AdvancedBA\project\Critical-Energy-Infrastructure-Under-Hybrid-War-Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365A0E68-7859-4853-BB1A-DE7DE2FB6251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDB58C6-5190-4A87-9251-C93E03B72468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="1335" windowWidth="17025" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11162" uniqueCount="4010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11170" uniqueCount="4016">
   <si>
     <t>Bus Data</t>
   </si>
@@ -12058,6 +12058,24 @@
   </si>
   <si>
     <t>lat</t>
+  </si>
+  <si>
+    <t>Flaged</t>
+  </si>
+  <si>
+    <t>flgged</t>
+  </si>
+  <si>
+    <t>flagged</t>
+  </si>
+  <si>
+    <t>kan ikke ses</t>
+  </si>
+  <si>
+    <t>tjek om lokation visuelt passer</t>
+  </si>
+  <si>
+    <t>not a station?</t>
   </si>
 </sst>
 </file>
@@ -12340,7 +12358,7 @@
   <cols>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="36.5703125" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="10.140625" customWidth="1"/>
@@ -12741,7 +12759,7 @@
         <v>55.883299999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>199</v>
       </c>
@@ -12770,7 +12788,7 @@
         <v>55.883299999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>198</v>
       </c>
@@ -12799,7 +12817,7 @@
         <v>55.883299999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>59</v>
       </c>
@@ -12828,7 +12846,7 @@
         <v>55.661299999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>60</v>
       </c>
@@ -12857,7 +12875,7 @@
         <v>55.661299999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>61</v>
       </c>
@@ -12886,7 +12904,7 @@
         <v>55.661299999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>62</v>
       </c>
@@ -12915,7 +12933,7 @@
         <v>55.661299999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>63</v>
       </c>
@@ -12944,7 +12962,7 @@
         <v>55.661299999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>64</v>
       </c>
@@ -12973,7 +12991,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>65</v>
       </c>
@@ -13002,7 +13020,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>66</v>
       </c>
@@ -13031,7 +13049,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>67</v>
       </c>
@@ -13060,7 +13078,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>68</v>
       </c>
@@ -13089,7 +13107,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>69</v>
       </c>
@@ -13118,7 +13136,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>70</v>
       </c>
@@ -13147,7 +13165,7 @@
         <v>55.6036</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -13166,10 +13184,17 @@
       <c r="G31" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H31" s="1">
+        <v>9.4109070012502993</v>
+      </c>
+      <c r="I31" s="1">
+        <v>54.780122278581999</v>
+      </c>
+      <c r="J31" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>71</v>
       </c>
@@ -13662,7 +13687,7 @@
         <v>55.643999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>5</v>
       </c>
@@ -13681,10 +13706,17 @@
       <c r="G49" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H49" s="1">
+        <v>9.4109070012502993</v>
+      </c>
+      <c r="I49" s="1">
+        <v>54.780122278581999</v>
+      </c>
+      <c r="J49" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>85</v>
       </c>
@@ -13706,10 +13738,14 @@
       <c r="G50" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H50" s="1">
+        <v>12.0134706285218</v>
+      </c>
+      <c r="I50" s="1">
+        <v>55.967703672425301</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>86</v>
       </c>
@@ -13731,10 +13767,14 @@
       <c r="G51" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H51" s="1">
+        <v>12.0134706285218</v>
+      </c>
+      <c r="I51" s="1">
+        <v>55.967703672425301</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>207</v>
       </c>
@@ -13763,7 +13803,7 @@
         <v>57.278810786117198</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>87</v>
       </c>
@@ -13792,7 +13832,7 @@
         <v>55.747187804005499</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>146</v>
       </c>
@@ -13821,7 +13861,7 @@
         <v>55.680999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>88</v>
       </c>
@@ -13850,7 +13890,7 @@
         <v>55.7020042516207</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>208</v>
       </c>
@@ -13879,7 +13919,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>209</v>
       </c>
@@ -13908,7 +13948,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>210</v>
       </c>
@@ -13937,7 +13977,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>211</v>
       </c>
@@ -13966,7 +14006,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>212</v>
       </c>
@@ -13995,7 +14035,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>213</v>
       </c>
@@ -14024,7 +14064,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>214</v>
       </c>
@@ -14053,7 +14093,7 @@
         <v>55.606999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>89</v>
       </c>
@@ -14082,7 +14122,7 @@
         <v>54.854999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>215</v>
       </c>
@@ -14111,7 +14151,7 @@
         <v>55.463453583519602</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>90</v>
       </c>
@@ -14140,7 +14180,7 @@
         <v>54.667257021721198</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>216</v>
       </c>
@@ -14169,7 +14209,7 @@
         <v>56.994184797429099</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>217</v>
       </c>
@@ -14198,7 +14238,7 @@
         <v>56.994184797429099</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>218</v>
       </c>
@@ -14227,7 +14267,7 @@
         <v>55.363999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>219</v>
       </c>
@@ -14256,7 +14296,7 @@
         <v>55.363999999999997</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>220</v>
       </c>
@@ -14285,7 +14325,7 @@
         <v>55.363999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>221</v>
       </c>
@@ -14314,7 +14354,7 @@
         <v>55.363999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>91</v>
       </c>
@@ -14343,7 +14383,7 @@
         <v>55.599077862221797</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>6</v>
       </c>
@@ -14362,10 +14402,17 @@
       <c r="G73" t="s">
         <v>14</v>
       </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H73" s="1">
+        <v>9.4109070012502993</v>
+      </c>
+      <c r="I73" s="1">
+        <v>54.780122278581999</v>
+      </c>
+      <c r="J73" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>92</v>
       </c>
@@ -14394,7 +14441,7 @@
         <v>55.28</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>226</v>
       </c>
@@ -14423,7 +14470,7 @@
         <v>57.1606374862682</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>227</v>
       </c>
@@ -14452,7 +14499,7 @@
         <v>57.122999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>228</v>
       </c>
@@ -14481,7 +14528,7 @@
         <v>57.122999999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>229</v>
       </c>
@@ -14510,7 +14557,7 @@
         <v>55.444983096760403</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>230</v>
       </c>
@@ -14539,7 +14586,7 @@
         <v>55.444983096760403</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>231</v>
       </c>
@@ -15835,8 +15882,12 @@
       <c r="G124" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
+      <c r="H124" s="1">
+        <v>9.2004788539427604</v>
+      </c>
+      <c r="I124" s="1">
+        <v>54.842137804197797</v>
+      </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
@@ -16759,8 +16810,12 @@
       <c r="G156" t="s">
         <v>14</v>
       </c>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
+      <c r="H156" s="1">
+        <v>10.0433043328441</v>
+      </c>
+      <c r="I156" s="1">
+        <v>56.186777773436603</v>
+      </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
@@ -16878,7 +16933,7 @@
         <v>55.838999999999999</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>265</v>
       </c>
@@ -16907,7 +16962,7 @@
         <v>55.470870841374499</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>266</v>
       </c>
@@ -16936,7 +16991,7 @@
         <v>55.262</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>267</v>
       </c>
@@ -16965,7 +17020,7 @@
         <v>56.036000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>268</v>
       </c>
@@ -16994,7 +17049,7 @@
         <v>56.036000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>149</v>
       </c>
@@ -17023,7 +17078,7 @@
         <v>55.003</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>269</v>
       </c>
@@ -17052,7 +17107,7 @@
         <v>56.435023192998003</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>270</v>
       </c>
@@ -17081,7 +17136,7 @@
         <v>56.26</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>271</v>
       </c>
@@ -17110,7 +17165,7 @@
         <v>56.26</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>272</v>
       </c>
@@ -17139,7 +17194,7 @@
         <v>56.26</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>273</v>
       </c>
@@ -17168,7 +17223,7 @@
         <v>56.26</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>274</v>
       </c>
@@ -17197,7 +17252,7 @@
         <v>56.225273912856998</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>275</v>
       </c>
@@ -17226,7 +17281,7 @@
         <v>56.429767245475198</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>276</v>
       </c>
@@ -17255,7 +17310,7 @@
         <v>56.875731729075802</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>150</v>
       </c>
@@ -17284,7 +17339,7 @@
         <v>55.568545162906503</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>177</v>
       </c>
@@ -17313,7 +17368,7 @@
         <v>56.022795688424402</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>0</v>
       </c>
@@ -17332,10 +17387,17 @@
       <c r="G176" t="s">
         <v>14</v>
       </c>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H176" s="1">
+        <v>12.8780796702535</v>
+      </c>
+      <c r="I176" s="1">
+        <v>56.077813921158103</v>
+      </c>
+      <c r="J176" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1</v>
       </c>
@@ -17354,10 +17416,17 @@
       <c r="G177" t="s">
         <v>14</v>
       </c>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H177" s="1">
+        <v>12.8780796702535</v>
+      </c>
+      <c r="I177" s="1">
+        <v>56.077813921158103</v>
+      </c>
+      <c r="J177" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>151</v>
       </c>
@@ -17386,7 +17455,7 @@
         <v>55.756</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>152</v>
       </c>
@@ -17415,7 +17484,7 @@
         <v>55.87</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>8</v>
       </c>
@@ -17437,7 +17506,7 @@
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>277</v>
       </c>
@@ -17466,7 +17535,7 @@
         <v>57.030999999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>278</v>
       </c>
@@ -17495,7 +17564,7 @@
         <v>57.2835382606698</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>153</v>
       </c>
@@ -17524,7 +17593,7 @@
         <v>55.228999999999999</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>154</v>
       </c>
@@ -17553,7 +17622,7 @@
         <v>55.687374583797798</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>279</v>
       </c>
@@ -17582,7 +17651,7 @@
         <v>57.074343535788003</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>280</v>
       </c>
@@ -17611,7 +17680,7 @@
         <v>57.074343535788003</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>281</v>
       </c>
@@ -17640,7 +17709,7 @@
         <v>57.074343535788003</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>282</v>
       </c>
@@ -17669,7 +17738,7 @@
         <v>57.074343535788003</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>155</v>
       </c>
@@ -17691,10 +17760,17 @@
       <c r="G189" t="s">
         <v>14</v>
       </c>
-      <c r="H189" s="1"/>
-      <c r="I189" s="1"/>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H189" s="1">
+        <v>12.2940994932355</v>
+      </c>
+      <c r="I189" s="1">
+        <v>55.861675854758197</v>
+      </c>
+      <c r="J189" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>156</v>
       </c>
@@ -17716,10 +17792,17 @@
       <c r="G190" t="s">
         <v>14</v>
       </c>
-      <c r="H190" s="1"/>
-      <c r="I190" s="1"/>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H190" s="1">
+        <v>12.2940994932355</v>
+      </c>
+      <c r="I190" s="1">
+        <v>55.861675854758197</v>
+      </c>
+      <c r="J190" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>157</v>
       </c>
@@ -17748,7 +17831,7 @@
         <v>55.547121160443297</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>158</v>
       </c>
@@ -18495,8 +18578,12 @@
       <c r="G217" t="s">
         <v>14</v>
       </c>
-      <c r="H217" s="1"/>
-      <c r="I217" s="1"/>
+      <c r="H217" s="1">
+        <v>11.186215220130499</v>
+      </c>
+      <c r="I217" s="1">
+        <v>55.631358219696601</v>
+      </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
@@ -18520,8 +18607,12 @@
       <c r="G218" t="s">
         <v>14</v>
       </c>
-      <c r="H218" s="1"/>
-      <c r="I218" s="1"/>
+      <c r="H218" s="1">
+        <v>12.0571224673565</v>
+      </c>
+      <c r="I218" s="1">
+        <v>55.516213557079098</v>
+      </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
@@ -18545,8 +18636,12 @@
       <c r="G219" t="s">
         <v>14</v>
       </c>
-      <c r="H219" s="1"/>
-      <c r="I219" s="1"/>
+      <c r="H219" s="1">
+        <v>12.1786411808216</v>
+      </c>
+      <c r="I219" s="1">
+        <v>55.810061876686198</v>
+      </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
@@ -18628,8 +18723,12 @@
       <c r="G222" t="s">
         <v>22</v>
       </c>
-      <c r="H222" s="1"/>
-      <c r="I222" s="1"/>
+      <c r="H222" s="1">
+        <v>8.5321392363917301</v>
+      </c>
+      <c r="I222" s="1">
+        <v>55.9837676021059</v>
+      </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
@@ -18653,8 +18752,12 @@
       <c r="G223" t="s">
         <v>31</v>
       </c>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1"/>
+      <c r="H223" s="1">
+        <v>11.118692777760799</v>
+      </c>
+      <c r="I223" s="1">
+        <v>55.659048389991703</v>
+      </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
@@ -19049,8 +19152,12 @@
       <c r="G237" t="s">
         <v>22</v>
       </c>
-      <c r="H237" s="1"/>
-      <c r="I237" s="1"/>
+      <c r="H237" s="1">
+        <v>9.5543728944980693</v>
+      </c>
+      <c r="I237" s="1">
+        <v>56.573406951323399</v>
+      </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
@@ -19139,7 +19246,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>178</v>
       </c>
@@ -19161,10 +19268,14 @@
       <c r="G241" t="s">
         <v>140</v>
       </c>
-      <c r="H241" s="1"/>
-      <c r="I241" s="1"/>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H241" s="1">
+        <v>12.1116093655294</v>
+      </c>
+      <c r="I241" s="1">
+        <v>55.420265084760402</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>179</v>
       </c>
@@ -19186,10 +19297,14 @@
       <c r="G242" t="s">
         <v>14</v>
       </c>
-      <c r="H242" s="1"/>
-      <c r="I242" s="1"/>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H242" s="1">
+        <v>12.2514785270647</v>
+      </c>
+      <c r="I242" s="1">
+        <v>55.626134546686799</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>321</v>
       </c>
@@ -19218,7 +19333,7 @@
         <v>56.252000000000002</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>322</v>
       </c>
@@ -19247,7 +19362,7 @@
         <v>56.252000000000002</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>323</v>
       </c>
@@ -19276,7 +19391,7 @@
         <v>56.252000000000002</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>9</v>
       </c>
@@ -19297,8 +19412,11 @@
       </c>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J246" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>21</v>
       </c>
@@ -19320,10 +19438,14 @@
       <c r="G247" t="s">
         <v>22</v>
       </c>
-      <c r="H247" s="1"/>
-      <c r="I247" s="1"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H247" s="1">
+        <v>9.4367825955821996</v>
+      </c>
+      <c r="I247" s="1">
+        <v>54.784723282375303</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>180</v>
       </c>
@@ -19352,7 +19474,7 @@
         <v>55.972999999999999</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>182</v>
       </c>
@@ -19381,7 +19503,7 @@
         <v>55.656374272645202</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>324</v>
       </c>
@@ -19410,7 +19532,7 @@
         <v>57.067</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>325</v>
       </c>
@@ -19432,10 +19554,14 @@
       <c r="G251" t="s">
         <v>22</v>
       </c>
-      <c r="H251" s="1"/>
-      <c r="I251" s="1"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H251" s="1">
+        <v>10.1253547905537</v>
+      </c>
+      <c r="I251" s="1">
+        <v>57.110090180481897</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>326</v>
       </c>
@@ -19464,7 +19590,7 @@
         <v>57.067</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>327</v>
       </c>
@@ -19493,7 +19619,7 @@
         <v>57.067</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>335</v>
       </c>
@@ -19522,7 +19648,7 @@
         <v>56.087000000000003</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>183</v>
       </c>
@@ -19551,7 +19677,7 @@
         <v>55.665999999999997</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>336</v>
       </c>
@@ -19631,8 +19757,12 @@
       <c r="G258" t="s">
         <v>22</v>
       </c>
-      <c r="H258" s="1"/>
-      <c r="I258" s="1"/>
+      <c r="H258" s="1">
+        <v>8.4646001465930105</v>
+      </c>
+      <c r="I258" s="1">
+        <v>55.524270683867798</v>
+      </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
@@ -19656,8 +19786,12 @@
       <c r="G259" t="s">
         <v>22</v>
       </c>
-      <c r="H259" s="1"/>
-      <c r="I259" s="1"/>
+      <c r="H259" s="1">
+        <v>8.4646001465930105</v>
+      </c>
+      <c r="I259" s="1">
+        <v>55.524270683867798</v>
+      </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
@@ -19681,8 +19815,12 @@
       <c r="G260" t="s">
         <v>22</v>
       </c>
-      <c r="H260" s="1"/>
-      <c r="I260" s="1"/>
+      <c r="H260" s="1">
+        <v>8.4646001465930105</v>
+      </c>
+      <c r="I260" s="1">
+        <v>55.524270683867798</v>
+      </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261">
@@ -19764,8 +19902,12 @@
       <c r="G263" t="s">
         <v>14</v>
       </c>
-      <c r="H263" s="1"/>
-      <c r="I263" s="1"/>
+      <c r="H263" s="1">
+        <v>12.023999999999999</v>
+      </c>
+      <c r="I263" s="1">
+        <v>55.972999999999999</v>
+      </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264">
@@ -19852,7 +19994,6 @@
       <c r="G267" t="s">
         <v>14</v>
       </c>
-      <c r="H267" s="1"/>
       <c r="I267" s="1"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
@@ -20432,8 +20573,12 @@
       <c r="G292" t="s">
         <v>14</v>
       </c>
-      <c r="H292" s="1"/>
-      <c r="I292" s="1"/>
+      <c r="H292" s="1">
+        <v>10.9750155910519</v>
+      </c>
+      <c r="I292" s="1">
+        <v>55.3903923590996</v>
+      </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293">
@@ -20457,8 +20602,12 @@
       <c r="G293" t="s">
         <v>14</v>
       </c>
-      <c r="H293" s="1"/>
-      <c r="I293" s="1"/>
+      <c r="H293" s="1">
+        <v>10.9750155910519</v>
+      </c>
+      <c r="I293" s="1">
+        <v>55.3903923590996</v>
+      </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294">
@@ -20633,8 +20782,12 @@
       <c r="G300" t="s">
         <v>22</v>
       </c>
-      <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
+      <c r="H300" s="1">
+        <v>10.862594586913399</v>
+      </c>
+      <c r="I300" s="1">
+        <v>56.518542126271001</v>
+      </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301">
@@ -20762,12 +20915,12 @@
   <dimension ref="A1:L362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -39001,8 +39154,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">

--- a/publicdataexportv131450706334_with_lon_lat.xlsx
+++ b/publicdataexportv131450706334_with_lon_lat.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDB58C6-5190-4A87-9251-C93E03B72468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="1335" windowWidth="17025" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="1335" windowWidth="17025" windowHeight="14865" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
